--- a/XBRL-template-MFRS/11-Notes-AccountingPolicies.xlsx
+++ b/XBRL-template-MFRS/11-Notes-AccountingPolicies.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -43,6 +43,15 @@
     <font>
       <name val="Arial"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="3">
@@ -84,7 +93,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +107,12 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -473,12 +488,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>01/01/YYYY - 31/12/YYYY</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>01/01/YYYY - 31/12/YYYY</t>
         </is>

--- a/XBRL-template-MFRS/11-Notes-AccountingPolicies.xlsx
+++ b/XBRL-template-MFRS/11-Notes-AccountingPolicies.xlsx
@@ -16,8 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="7">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
+  </numFmts>
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -53,8 +55,37 @@
       <name val="Arial"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="006B7280"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -66,8 +97,14 @@
         <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8FAFC"/>
+        <bgColor rgb="00F8FAFC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -89,11 +126,21 @@
         <color rgb="00B0B0B0"/>
       </bottom>
     </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="001F3864"/>
+      </bottom>
+    </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="00D9DEE5"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -113,6 +160,27 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -479,518 +547,579 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C57"/>
+  <dimension ref="A1:D57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="B1" s="7" t="inlineStr">
+    <row r="1" ht="20" customHeight="1">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>01/01/YYYY - 31/12/YYYY</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="8" t="inlineStr">
         <is>
           <t>01/01/YYYY - 31/12/YYYY</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="D1" s="13" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>Notes - Summary of material accounting policies</t>
         </is>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="D3" s="9" t="n"/>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>*Disclosure of material accounting policy information</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="4" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="B4" s="11" t="n"/>
+      <c r="C4" s="11" t="n"/>
+      <c r="D4" s="14" t="n"/>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Description of accounting policy for biological assets</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n"/>
-      <c r="C5" s="4" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="B5" s="11" t="n"/>
+      <c r="C5" s="11" t="n"/>
+      <c r="D5" s="14" t="n"/>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Description of accounting policy for borrowing costs</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n"/>
-      <c r="C6" s="4" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="B6" s="11" t="n"/>
+      <c r="C6" s="11" t="n"/>
+      <c r="D6" s="14" t="n"/>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>Description of accounting policy for borrowings</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n"/>
-      <c r="C7" s="4" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="B7" s="11" t="n"/>
+      <c r="C7" s="11" t="n"/>
+      <c r="D7" s="14" t="n"/>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>Description of accounting policy for business combinations</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n"/>
-      <c r="C8" s="4" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="B8" s="11" t="n"/>
+      <c r="C8" s="11" t="n"/>
+      <c r="D8" s="14" t="n"/>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>Description of accounting policy for cash and cash equivalents</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n"/>
-      <c r="C9" s="4" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="B9" s="11" t="n"/>
+      <c r="C9" s="11" t="n"/>
+      <c r="D9" s="14" t="n"/>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>Description of accounting policy for commodity future and forward contracts</t>
         </is>
       </c>
-      <c r="B10" s="4" t="n"/>
-      <c r="C10" s="4" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="B10" s="11" t="n"/>
+      <c r="C10" s="11" t="n"/>
+      <c r="D10" s="14" t="n"/>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>Description of accounting policy for construction contracts</t>
         </is>
       </c>
-      <c r="B11" s="4" t="n"/>
-      <c r="C11" s="4" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="B11" s="11" t="n"/>
+      <c r="C11" s="11" t="n"/>
+      <c r="D11" s="14" t="n"/>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>Description of accounting policy for construction in progress</t>
         </is>
       </c>
-      <c r="B12" s="4" t="n"/>
-      <c r="C12" s="4" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="B12" s="11" t="n"/>
+      <c r="C12" s="11" t="n"/>
+      <c r="D12" s="14" t="n"/>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>Description of accounting policy for contingent liabilities and contingent assets</t>
         </is>
       </c>
-      <c r="B13" s="4" t="n"/>
-      <c r="C13" s="4" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="B13" s="11" t="n"/>
+      <c r="C13" s="11" t="n"/>
+      <c r="D13" s="14" t="n"/>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>Description of accounting policy for customer loyalty programmes</t>
         </is>
       </c>
-      <c r="B14" s="4" t="n"/>
-      <c r="C14" s="4" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B14" s="11" t="n"/>
+      <c r="C14" s="11" t="n"/>
+      <c r="D14" s="14" t="n"/>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>Description of accounting policy for decommissioning, restoration and rehabilitation provisions</t>
         </is>
       </c>
-      <c r="B15" s="4" t="n"/>
-      <c r="C15" s="4" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="B15" s="11" t="n"/>
+      <c r="C15" s="11" t="n"/>
+      <c r="D15" s="14" t="n"/>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t>Description of accounting policy for deferred income tax</t>
         </is>
       </c>
-      <c r="B16" s="4" t="n"/>
-      <c r="C16" s="4" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="B16" s="11" t="n"/>
+      <c r="C16" s="11" t="n"/>
+      <c r="D16" s="14" t="n"/>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="12" t="inlineStr">
         <is>
           <t>Description of accounting policy for depreciation expense</t>
         </is>
       </c>
-      <c r="B17" s="4" t="n"/>
-      <c r="C17" s="4" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="B17" s="11" t="n"/>
+      <c r="C17" s="11" t="n"/>
+      <c r="D17" s="14" t="n"/>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>Description of accounting policy for discontinued operations</t>
         </is>
       </c>
-      <c r="B18" s="4" t="n"/>
-      <c r="C18" s="4" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="B18" s="11" t="n"/>
+      <c r="C18" s="11" t="n"/>
+      <c r="D18" s="14" t="n"/>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="12" t="inlineStr">
         <is>
           <t>Description of accounting policy for dividend income</t>
         </is>
       </c>
-      <c r="B19" s="4" t="n"/>
-      <c r="C19" s="4" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="B19" s="11" t="n"/>
+      <c r="C19" s="11" t="n"/>
+      <c r="D19" s="14" t="n"/>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="12" t="inlineStr">
         <is>
           <t>Description of accounting policy for earnings per share</t>
         </is>
       </c>
-      <c r="B20" s="4" t="n"/>
-      <c r="C20" s="4" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="B20" s="11" t="n"/>
+      <c r="C20" s="11" t="n"/>
+      <c r="D20" s="14" t="n"/>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="12" t="inlineStr">
         <is>
           <t>Description of accounting policy for emission rights</t>
         </is>
       </c>
-      <c r="B21" s="4" t="n"/>
-      <c r="C21" s="4" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="B21" s="11" t="n"/>
+      <c r="C21" s="11" t="n"/>
+      <c r="D21" s="14" t="n"/>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="12" t="inlineStr">
         <is>
           <t>Description of accounting policy for employee benefits</t>
         </is>
       </c>
-      <c r="B22" s="4" t="n"/>
-      <c r="C22" s="4" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="B22" s="11" t="n"/>
+      <c r="C22" s="11" t="n"/>
+      <c r="D22" s="14" t="n"/>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="12" t="inlineStr">
         <is>
           <t>Description of accounting policy for equity instruments</t>
         </is>
       </c>
-      <c r="B23" s="4" t="n"/>
-      <c r="C23" s="4" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="B23" s="11" t="n"/>
+      <c r="C23" s="11" t="n"/>
+      <c r="D23" s="14" t="n"/>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="12" t="inlineStr">
         <is>
           <t>Description of accounting policy for exploration and development expenditures</t>
         </is>
       </c>
-      <c r="B24" s="4" t="n"/>
-      <c r="C24" s="4" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="B24" s="11" t="n"/>
+      <c r="C24" s="11" t="n"/>
+      <c r="D24" s="14" t="n"/>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="12" t="inlineStr">
         <is>
           <t>Description of accounting policy for fair value measurement</t>
         </is>
       </c>
-      <c r="B25" s="4" t="n"/>
-      <c r="C25" s="4" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="B25" s="11" t="n"/>
+      <c r="C25" s="11" t="n"/>
+      <c r="D25" s="14" t="n"/>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="12" t="inlineStr">
         <is>
           <t>Description of accounting policy for finance income and costs</t>
         </is>
       </c>
-      <c r="B26" s="4" t="n"/>
-      <c r="C26" s="4" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="B26" s="11" t="n"/>
+      <c r="C26" s="11" t="n"/>
+      <c r="D26" s="14" t="n"/>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
         <is>
           <t>Description of accounting policy for financial instruments</t>
         </is>
       </c>
-      <c r="B27" s="4" t="n"/>
-      <c r="C27" s="4" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="B27" s="11" t="n"/>
+      <c r="C27" s="11" t="n"/>
+      <c r="D27" s="14" t="n"/>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
         <is>
           <t>Description of accounting policy for foreign currencies</t>
         </is>
       </c>
-      <c r="B28" s="4" t="n"/>
-      <c r="C28" s="4" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="B28" s="11" t="n"/>
+      <c r="C28" s="11" t="n"/>
+      <c r="D28" s="14" t="n"/>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="12" t="inlineStr">
         <is>
           <t>Description of accounting policy for goodwill</t>
         </is>
       </c>
-      <c r="B29" s="4" t="n"/>
-      <c r="C29" s="4" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="B29" s="11" t="n"/>
+      <c r="C29" s="11" t="n"/>
+      <c r="D29" s="14" t="n"/>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="12" t="inlineStr">
         <is>
           <t>Description of accounting policy for government grants</t>
         </is>
       </c>
-      <c r="B30" s="4" t="n"/>
-      <c r="C30" s="4" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="B30" s="11" t="n"/>
+      <c r="C30" s="11" t="n"/>
+      <c r="D30" s="14" t="n"/>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="12" t="inlineStr">
         <is>
           <t>Description of accounting policy for impairment of financial assets</t>
         </is>
       </c>
-      <c r="B31" s="4" t="n"/>
-      <c r="C31" s="4" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+      <c r="B31" s="11" t="n"/>
+      <c r="C31" s="11" t="n"/>
+      <c r="D31" s="14" t="n"/>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="12" t="inlineStr">
         <is>
           <t>Description of accounting policy for impairment of other assets</t>
         </is>
       </c>
-      <c r="B32" s="4" t="n"/>
-      <c r="C32" s="4" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
+      <c r="B32" s="11" t="n"/>
+      <c r="C32" s="11" t="n"/>
+      <c r="D32" s="14" t="n"/>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="12" t="inlineStr">
         <is>
           <t>Description of accounting policy for income tax</t>
         </is>
       </c>
-      <c r="B33" s="4" t="n"/>
-      <c r="C33" s="4" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
+      <c r="B33" s="11" t="n"/>
+      <c r="C33" s="11" t="n"/>
+      <c r="D33" s="14" t="n"/>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="12" t="inlineStr">
         <is>
           <t>Description of accounting policy for intangible assets other than goodwill</t>
         </is>
       </c>
-      <c r="B34" s="4" t="n"/>
-      <c r="C34" s="4" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
+      <c r="B34" s="11" t="n"/>
+      <c r="C34" s="11" t="n"/>
+      <c r="D34" s="14" t="n"/>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="12" t="inlineStr">
         <is>
           <t>Description of accounting policy for interest income and expense</t>
         </is>
       </c>
-      <c r="B35" s="4" t="n"/>
-      <c r="C35" s="4" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
+      <c r="B35" s="11" t="n"/>
+      <c r="C35" s="11" t="n"/>
+      <c r="D35" s="14" t="n"/>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="12" t="inlineStr">
         <is>
           <t>Description of accounting policy for inventories</t>
         </is>
       </c>
-      <c r="B36" s="4" t="n"/>
-      <c r="C36" s="4" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
+      <c r="B36" s="11" t="n"/>
+      <c r="C36" s="11" t="n"/>
+      <c r="D36" s="14" t="n"/>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="12" t="inlineStr">
         <is>
           <t>Description of accounting policy for investment in associates</t>
         </is>
       </c>
-      <c r="B37" s="4" t="n"/>
-      <c r="C37" s="4" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
+      <c r="B37" s="11" t="n"/>
+      <c r="C37" s="11" t="n"/>
+      <c r="D37" s="14" t="n"/>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="12" t="inlineStr">
         <is>
           <t>Description of accounting policy for investment property</t>
         </is>
       </c>
-      <c r="B38" s="4" t="n"/>
-      <c r="C38" s="4" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
+      <c r="B38" s="11" t="n"/>
+      <c r="C38" s="11" t="n"/>
+      <c r="D38" s="14" t="n"/>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="12" t="inlineStr">
         <is>
           <t>Description of accounting policy for investments in joint arrangements</t>
         </is>
       </c>
-      <c r="B39" s="4" t="n"/>
-      <c r="C39" s="4" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
+      <c r="B39" s="11" t="n"/>
+      <c r="C39" s="11" t="n"/>
+      <c r="D39" s="14" t="n"/>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="12" t="inlineStr">
         <is>
           <t>Description of accounting policy for investments in subsidiaries</t>
         </is>
       </c>
-      <c r="B40" s="4" t="n"/>
-      <c r="C40" s="4" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
+      <c r="B40" s="11" t="n"/>
+      <c r="C40" s="11" t="n"/>
+      <c r="D40" s="14" t="n"/>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="12" t="inlineStr">
         <is>
           <t>Description of accounting policy for irredeemable convertible unsecured loan stocks (“ICULS”)</t>
         </is>
       </c>
-      <c r="B41" s="4" t="n"/>
-      <c r="C41" s="4" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="5" t="inlineStr">
+      <c r="B41" s="11" t="n"/>
+      <c r="C41" s="11" t="n"/>
+      <c r="D41" s="14" t="n"/>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="12" t="inlineStr">
         <is>
           <t>Description of accounting policy for leases</t>
         </is>
       </c>
-      <c r="B42" s="4" t="n"/>
-      <c r="C42" s="4" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
+      <c r="B42" s="11" t="n"/>
+      <c r="C42" s="11" t="n"/>
+      <c r="D42" s="14" t="n"/>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="12" t="inlineStr">
         <is>
           <t>Description of accounting policy for loss of control</t>
         </is>
       </c>
-      <c r="B43" s="4" t="n"/>
-      <c r="C43" s="4" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="5" t="inlineStr">
+      <c r="B43" s="11" t="n"/>
+      <c r="C43" s="11" t="n"/>
+      <c r="D43" s="14" t="n"/>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="A44" s="12" t="inlineStr">
         <is>
           <t>Description of accounting policy for non-current assets or disposal groups classified as held for sale</t>
         </is>
       </c>
-      <c r="B44" s="4" t="n"/>
-      <c r="C44" s="4" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="5" t="inlineStr">
+      <c r="B44" s="11" t="n"/>
+      <c r="C44" s="11" t="n"/>
+      <c r="D44" s="14" t="n"/>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="A45" s="12" t="inlineStr">
         <is>
           <t>Description of accounting policy for operating segment reporting</t>
         </is>
       </c>
-      <c r="B45" s="4" t="n"/>
-      <c r="C45" s="4" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
+      <c r="B45" s="11" t="n"/>
+      <c r="C45" s="11" t="n"/>
+      <c r="D45" s="14" t="n"/>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="A46" s="12" t="inlineStr">
         <is>
           <t>Description of accounting policy for other provisions</t>
         </is>
       </c>
-      <c r="B46" s="4" t="n"/>
-      <c r="C46" s="4" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="5" t="inlineStr">
+      <c r="B46" s="11" t="n"/>
+      <c r="C46" s="11" t="n"/>
+      <c r="D46" s="14" t="n"/>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="A47" s="12" t="inlineStr">
         <is>
           <t>Description of accounting policy for property development costs</t>
         </is>
       </c>
-      <c r="B47" s="4" t="n"/>
-      <c r="C47" s="4" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="5" t="inlineStr">
+      <c r="B47" s="11" t="n"/>
+      <c r="C47" s="11" t="n"/>
+      <c r="D47" s="14" t="n"/>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="A48" s="12" t="inlineStr">
         <is>
           <t>Description of accounting policy for property, plant and equipment</t>
         </is>
       </c>
-      <c r="B48" s="4" t="n"/>
-      <c r="C48" s="4" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
+      <c r="B48" s="11" t="n"/>
+      <c r="C48" s="11" t="n"/>
+      <c r="D48" s="14" t="n"/>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="A49" s="12" t="inlineStr">
         <is>
           <t>Description of accounting policy for recognition of revenue and other income</t>
         </is>
       </c>
-      <c r="B49" s="4" t="n"/>
-      <c r="C49" s="4" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="5" t="inlineStr">
+      <c r="B49" s="11" t="n"/>
+      <c r="C49" s="11" t="n"/>
+      <c r="D49" s="14" t="n"/>
+    </row>
+    <row r="50" ht="18" customHeight="1">
+      <c r="A50" s="12" t="inlineStr">
         <is>
           <t>Description of accounting policy for research and development expense</t>
         </is>
       </c>
-      <c r="B50" s="4" t="n"/>
-      <c r="C50" s="4" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="5" t="inlineStr">
+      <c r="B50" s="11" t="n"/>
+      <c r="C50" s="11" t="n"/>
+      <c r="D50" s="14" t="n"/>
+    </row>
+    <row r="51" ht="18" customHeight="1">
+      <c r="A51" s="12" t="inlineStr">
         <is>
           <t>Description of accounting policy for share capital</t>
         </is>
       </c>
-      <c r="B51" s="4" t="n"/>
-      <c r="C51" s="4" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
+      <c r="B51" s="11" t="n"/>
+      <c r="C51" s="11" t="n"/>
+      <c r="D51" s="14" t="n"/>
+    </row>
+    <row r="52" ht="18" customHeight="1">
+      <c r="A52" s="12" t="inlineStr">
         <is>
           <t>Description of accounting policy for share-based payment transactions</t>
         </is>
       </c>
-      <c r="B52" s="4" t="n"/>
-      <c r="C52" s="4" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="5" t="inlineStr">
+      <c r="B52" s="11" t="n"/>
+      <c r="C52" s="11" t="n"/>
+      <c r="D52" s="14" t="n"/>
+    </row>
+    <row r="53" ht="18" customHeight="1">
+      <c r="A53" s="12" t="inlineStr">
         <is>
           <t>Description of accounting policy for transactions with non-controlling interests</t>
         </is>
       </c>
-      <c r="B53" s="4" t="n"/>
-      <c r="C53" s="4" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr">
+      <c r="B53" s="11" t="n"/>
+      <c r="C53" s="11" t="n"/>
+      <c r="D53" s="14" t="n"/>
+    </row>
+    <row r="54" ht="18" customHeight="1">
+      <c r="A54" s="12" t="inlineStr">
         <is>
           <t>Description of accounting policy for transactions with related parties</t>
         </is>
       </c>
-      <c r="B54" s="4" t="n"/>
-      <c r="C54" s="4" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
+      <c r="B54" s="11" t="n"/>
+      <c r="C54" s="11" t="n"/>
+      <c r="D54" s="14" t="n"/>
+    </row>
+    <row r="55" ht="18" customHeight="1">
+      <c r="A55" s="12" t="inlineStr">
         <is>
           <t>Description of accounting policy for treasury shares</t>
         </is>
       </c>
-      <c r="B55" s="4" t="n"/>
-      <c r="C55" s="4" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="5" t="inlineStr">
+      <c r="B55" s="11" t="n"/>
+      <c r="C55" s="11" t="n"/>
+      <c r="D55" s="14" t="n"/>
+    </row>
+    <row r="56" ht="18" customHeight="1">
+      <c r="A56" s="12" t="inlineStr">
         <is>
           <t>Description of accounting policy for warrants</t>
         </is>
       </c>
-      <c r="B56" s="4" t="n"/>
-      <c r="C56" s="4" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="5" t="inlineStr">
+      <c r="B56" s="11" t="n"/>
+      <c r="C56" s="11" t="n"/>
+      <c r="D56" s="14" t="n"/>
+    </row>
+    <row r="57" ht="18" customHeight="1">
+      <c r="A57" s="12" t="inlineStr">
         <is>
           <t>Description of other material accounting policies relevant to understanding of financial statements</t>
         </is>
       </c>
-      <c r="B57" s="4" t="n"/>
-      <c r="C57" s="4" t="n"/>
+      <c r="B57" s="11" t="n"/>
+      <c r="C57" s="11" t="n"/>
+      <c r="D57" s="14" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
